--- a/public/abc2/material/finanzas-cheques.xlsx
+++ b/public/abc2/material/finanzas-cheques.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,15 +413,18 @@
         <v>Monto</v>
       </c>
       <c r="E1" t="str">
+        <v>Emisión</v>
+      </c>
+      <c r="F1" t="str">
         <v>Vencimiento</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Estado</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>0041231</v>
+        <v>0041000</v>
       </c>
       <c r="B2" t="str">
         <v>Nación</v>
@@ -430,18 +433,21 @@
         <v>Distribuidora Sur SA</v>
       </c>
       <c r="D2">
-        <v>850000</v>
+        <v>90000</v>
       </c>
       <c r="E2" t="str">
-        <v>05/07/2026</v>
+        <v>01/06/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>A cobrar</v>
+        <v>01/07/2026</v>
+      </c>
+      <c r="G2" t="str">
+        <v>VENCIDO</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0087554</v>
+        <v>0041137</v>
       </c>
       <c r="B3" t="str">
         <v>Galicia</v>
@@ -450,18 +456,21 @@
         <v>Kiosco El Rápido</v>
       </c>
       <c r="D3">
-        <v>120000</v>
+        <v>867000</v>
       </c>
       <c r="E3" t="str">
+        <v>02/06/2026</v>
+      </c>
+      <c r="F3" t="str">
         <v>08/07/2026</v>
       </c>
-      <c r="F3" t="str">
-        <v>A cobrar</v>
+      <c r="G3" t="str">
+        <v>Próximo</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>0012090</v>
+        <v>0041274</v>
       </c>
       <c r="B4" t="str">
         <v>Macro</v>
@@ -470,18 +479,21 @@
         <v>Ferretería Pérez</v>
       </c>
       <c r="D4">
-        <v>340000</v>
+        <v>804000</v>
       </c>
       <c r="E4" t="str">
-        <v>03/07/2026</v>
+        <v>03/06/2026</v>
       </c>
       <c r="F4" t="str">
-        <v>VENCIDO</v>
+        <v>15/07/2026</v>
+      </c>
+      <c r="G4" t="str">
+        <v>A cobrar</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0099821</v>
+        <v>0041411</v>
       </c>
       <c r="B5" t="str">
         <v>BBVA</v>
@@ -490,18 +502,21 @@
         <v>Almacén Doña Rosa</v>
       </c>
       <c r="D5">
-        <v>210000</v>
+        <v>741000</v>
       </c>
       <c r="E5" t="str">
-        <v>12/07/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="F5" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="G5" t="str">
         <v>A cobrar</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0055012</v>
+        <v>0041548</v>
       </c>
       <c r="B6" t="str">
         <v>Santander</v>
@@ -510,18 +525,596 @@
         <v>Taller Gómez</v>
       </c>
       <c r="D6">
-        <v>480000</v>
+        <v>678000</v>
       </c>
       <c r="E6" t="str">
-        <v>06/07/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="F6" t="str">
-        <v>A cobrar</v>
+        <v>01/07/2026</v>
+      </c>
+      <c r="G6" t="str">
+        <v>VENCIDO</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>0041685</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Provincia</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Panadería La Espiga</v>
+      </c>
+      <c r="D7">
+        <v>615000</v>
+      </c>
+      <c r="E7" t="str">
+        <v>06/06/2026</v>
+      </c>
+      <c r="F7" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Próximo</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>0041822</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Credicoop</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Corralón San Juan</v>
+      </c>
+      <c r="D8">
+        <v>552000</v>
+      </c>
+      <c r="E8" t="str">
+        <v>07/06/2026</v>
+      </c>
+      <c r="F8" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="G8" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>0041959</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Comafi</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Farmacia del Centro</v>
+      </c>
+      <c r="D9">
+        <v>489000</v>
+      </c>
+      <c r="E9" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="F9" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="G9" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>0042096</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Nación</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Verdulería Norte</v>
+      </c>
+      <c r="D10">
+        <v>426000</v>
+      </c>
+      <c r="E10" t="str">
+        <v>09/06/2026</v>
+      </c>
+      <c r="F10" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="G10" t="str">
+        <v>VENCIDO</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>0042233</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Galicia</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Librería Pizarrón</v>
+      </c>
+      <c r="D11">
+        <v>363000</v>
+      </c>
+      <c r="E11" t="str">
+        <v>10/06/2026</v>
+      </c>
+      <c r="F11" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Próximo</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>0042370</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Macro</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Distribuidora Sur SA</v>
+      </c>
+      <c r="D12">
+        <v>300000</v>
+      </c>
+      <c r="E12" t="str">
+        <v>11/06/2026</v>
+      </c>
+      <c r="F12" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="G12" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>0042507</v>
+      </c>
+      <c r="B13" t="str">
+        <v>BBVA</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Kiosco El Rápido</v>
+      </c>
+      <c r="D13">
+        <v>237000</v>
+      </c>
+      <c r="E13" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="F13" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="G13" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>0042644</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Santander</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Ferretería Pérez</v>
+      </c>
+      <c r="D14">
+        <v>174000</v>
+      </c>
+      <c r="E14" t="str">
+        <v>13/06/2026</v>
+      </c>
+      <c r="F14" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="G14" t="str">
+        <v>VENCIDO</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>0042781</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Provincia</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Almacén Doña Rosa</v>
+      </c>
+      <c r="D15">
+        <v>111000</v>
+      </c>
+      <c r="E15" t="str">
+        <v>14/06/2026</v>
+      </c>
+      <c r="F15" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Próximo</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>0042918</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Credicoop</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Taller Gómez</v>
+      </c>
+      <c r="D16">
+        <v>888000</v>
+      </c>
+      <c r="E16" t="str">
+        <v>15/06/2026</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="G16" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>0043055</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Comafi</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Panadería La Espiga</v>
+      </c>
+      <c r="D17">
+        <v>825000</v>
+      </c>
+      <c r="E17" t="str">
+        <v>16/06/2026</v>
+      </c>
+      <c r="F17" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="G17" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>0043192</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Nación</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Corralón San Juan</v>
+      </c>
+      <c r="D18">
+        <v>762000</v>
+      </c>
+      <c r="E18" t="str">
+        <v>17/06/2026</v>
+      </c>
+      <c r="F18" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="G18" t="str">
+        <v>VENCIDO</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>0043329</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Galicia</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Farmacia del Centro</v>
+      </c>
+      <c r="D19">
+        <v>699000</v>
+      </c>
+      <c r="E19" t="str">
+        <v>18/06/2026</v>
+      </c>
+      <c r="F19" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Próximo</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>0043466</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Macro</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Verdulería Norte</v>
+      </c>
+      <c r="D20">
+        <v>636000</v>
+      </c>
+      <c r="E20" t="str">
+        <v>19/06/2026</v>
+      </c>
+      <c r="F20" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="G20" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>0043603</v>
+      </c>
+      <c r="B21" t="str">
+        <v>BBVA</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Librería Pizarrón</v>
+      </c>
+      <c r="D21">
+        <v>573000</v>
+      </c>
+      <c r="E21" t="str">
+        <v>20/06/2026</v>
+      </c>
+      <c r="F21" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="G21" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>0043740</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Santander</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Distribuidora Sur SA</v>
+      </c>
+      <c r="D22">
+        <v>510000</v>
+      </c>
+      <c r="E22" t="str">
+        <v>21/06/2026</v>
+      </c>
+      <c r="F22" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="G22" t="str">
+        <v>VENCIDO</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>0043877</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Provincia</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Kiosco El Rápido</v>
+      </c>
+      <c r="D23">
+        <v>447000</v>
+      </c>
+      <c r="E23" t="str">
+        <v>22/06/2026</v>
+      </c>
+      <c r="F23" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Próximo</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>0044014</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Credicoop</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Ferretería Pérez</v>
+      </c>
+      <c r="D24">
+        <v>384000</v>
+      </c>
+      <c r="E24" t="str">
+        <v>23/06/2026</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="G24" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>0044151</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Comafi</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Almacén Doña Rosa</v>
+      </c>
+      <c r="D25">
+        <v>321000</v>
+      </c>
+      <c r="E25" t="str">
+        <v>24/06/2026</v>
+      </c>
+      <c r="F25" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="G25" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>0044288</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Nación</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Taller Gómez</v>
+      </c>
+      <c r="D26">
+        <v>258000</v>
+      </c>
+      <c r="E26" t="str">
+        <v>25/06/2026</v>
+      </c>
+      <c r="F26" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="G26" t="str">
+        <v>VENCIDO</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>0044425</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Galicia</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Panadería La Espiga</v>
+      </c>
+      <c r="D27">
+        <v>195000</v>
+      </c>
+      <c r="E27" t="str">
+        <v>01/06/2026</v>
+      </c>
+      <c r="F27" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Próximo</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>0044562</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Macro</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Corralón San Juan</v>
+      </c>
+      <c r="D28">
+        <v>132000</v>
+      </c>
+      <c r="E28" t="str">
+        <v>02/06/2026</v>
+      </c>
+      <c r="F28" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="G28" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>0044699</v>
+      </c>
+      <c r="B29" t="str">
+        <v>BBVA</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Farmacia del Centro</v>
+      </c>
+      <c r="D29">
+        <v>909000</v>
+      </c>
+      <c r="E29" t="str">
+        <v>03/06/2026</v>
+      </c>
+      <c r="F29" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="G29" t="str">
+        <v>A cobrar</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>0044836</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Santander</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Verdulería Norte</v>
+      </c>
+      <c r="D30">
+        <v>846000</v>
+      </c>
+      <c r="E30" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="F30" t="str">
+        <v>01/07/2026</v>
+      </c>
+      <c r="G30" t="str">
+        <v>VENCIDO</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>0044973</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Provincia</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Librería Pizarrón</v>
+      </c>
+      <c r="D31">
+        <v>783000</v>
+      </c>
+      <c r="E31" t="str">
+        <v>05/06/2026</v>
+      </c>
+      <c r="F31" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Próximo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G31"/>
   </ignoredErrors>
 </worksheet>
 </file>